--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104500_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104500_W5.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6758</v>
+        <v>3.2015</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0189</v>
+        <v>3.4322</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.343</v>
+        <v>-0.2306</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5814</v>
+        <v>0.5608</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3682</v>
+        <v>0.354</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2132</v>
+        <v>0.2068</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4983</v>
+        <v>2.4389</v>
       </c>
       <c r="K2" t="n">
-        <v>2.621</v>
+        <v>2.5813</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1228</v>
+        <v>-0.1424</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9169</v>
+        <v>-1.8781</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2529</v>
+        <v>-2.2273</v>
       </c>
       <c r="O2" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0762</v>
+        <v>0.4828</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.13</v>
+        <v>0.3685</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0538</v>
+        <v>0.1143</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3975</v>
+        <v>2.3855</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4611</v>
+        <v>0.7755</v>
       </c>
       <c r="E3" t="n">
-        <v>1.961</v>
+        <v>1.3181</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4998</v>
+        <v>-0.5427</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1669</v>
+        <v>0.1718</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2223</v>
+        <v>-0.2185</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9232</v>
+        <v>0.9191</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2527</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1039</v>
+        <v>0.4689</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. LANGARITA</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1746</v>
+        <v>0.3575</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0173</v>
+        <v>-0.5313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1573</v>
+        <v>0.8888</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1746</v>
+        <v>-2.35</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0173</v>
+        <v>-6.4667</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1573</v>
+        <v>4.1166</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0173</v>
+        <v>-0.9746</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0173</v>
+        <v>-4.7421</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.7675</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1573</v>
+        <v>-1.3754</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.7246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1573</v>
+        <v>0.3492</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9592</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.2309</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0969</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.1595</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>L. LANGARITA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0434</v>
+        <v>0.1752</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8447</v>
+        <v>0.0172</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8013</v>
+        <v>0.1579</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3665</v>
+        <v>0.1752</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7086</v>
+        <v>0.0172</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6579</v>
+        <v>0.1579</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7045</v>
+        <v>0.0172</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5053</v>
+        <v>0.0172</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.2098</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.662</v>
+        <v>0.1579</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2139</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.1579</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7934</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4892</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3042</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4371</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2208</v>
+        <v>-0.1233</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6268</v>
+        <v>0.9174</v>
       </c>
       <c r="F6" t="n">
-        <v>0.406</v>
+        <v>-1.0407</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.593</v>
+        <v>0.333</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2496</v>
+        <v>-0.716</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3434</v>
+        <v>1.049</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7206</v>
+        <v>1.71</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7029</v>
+        <v>0.9653</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4234</v>
+        <v>0.7447</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8725</v>
+        <v>-1.377</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9525</v>
+        <v>-1.6813</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08</v>
+        <v>0.3043</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>1.172</v>
+        <v>-0.2382</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5474</v>
+        <v>-0.3373</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-1.3562</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0828</v>
+        <v>-0.9508</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0285</v>
+        <v>-1.2328</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1112</v>
+        <v>0.282</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3104</v>
+        <v>-2.5872</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7318</v>
+        <v>-1.2466</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0423</v>
+        <v>-1.3405</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7161</v>
+        <v>-0.7376</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9697</v>
+        <v>0.6927</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7463</v>
+        <v>-1.4303</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4056</v>
+        <v>-1.8496</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7016</v>
+        <v>-1.9394</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2959</v>
+        <v>0.0898</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1647</v>
+        <v>0.4283</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.234</v>
+        <v>-0.04</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0692</v>
+        <v>0.4683</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3627</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3627</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2992</v>
+        <v>-1.2584</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9249</v>
+        <v>-0.8038</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6257</v>
+        <v>-0.4546</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3124</v>
+        <v>-0.9749</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.4439</v>
+        <v>-0.2674</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1314</v>
+        <v>-0.7075</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8991</v>
+        <v>-0.6317</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.6946</v>
+        <v>0.1207</v>
       </c>
       <c r="L8" t="n">
-        <v>3.7955</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4133</v>
+        <v>-0.3432</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7493</v>
+        <v>-0.3881</v>
       </c>
       <c r="O8" t="n">
-        <v>0.336</v>
+        <v>0.0449</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9488</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.475</v>
+        <v>-0.1046</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3549</v>
+        <v>0.0556</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1201</v>
+        <v>-0.1601</v>
       </c>
       <c r="V8" t="n">
-        <v>3.1687</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>3.278</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1093</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6807</v>
+        <v>-1.9248</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.272</v>
+        <v>-2.577</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4087</v>
+        <v>0.6522</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9818</v>
+        <v>-2.3603</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2728</v>
+        <v>-0.7039</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.709</v>
+        <v>-1.6564</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6278</v>
+        <v>-1.7308</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1212</v>
+        <v>0.4891</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-2.22</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.354</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.394</v>
+        <v>-1.1931</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>0.5636</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0.9103</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>0.796</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.1143</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0.4358</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7739</v>
+        <v>-3.6996</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7572</v>
+        <v>-2.2727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9834000000000001</v>
+        <v>-1.4269</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2395</v>
+        <v>-2.4739</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5496</v>
+        <v>-2.3224</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.69</v>
+        <v>-0.1516</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.3096</v>
+        <v>-2.3471</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9506</v>
+        <v>-1.632</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3591</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0701</v>
+        <v>-0.1268</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.599</v>
+        <v>-0.6904</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6691</v>
+        <v>0.5636</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3315</v>
+        <v>-0.0547</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6866</v>
+        <v>0.5313</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3551</v>
+        <v>-0.586</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-3.2196</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-2.9904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0523</v>
+        <v>-4.0571</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4852</v>
+        <v>-5.1887</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5671</v>
+        <v>1.1316</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.461</v>
+        <v>-4.2508</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3012</v>
+        <v>-2.5585</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1599</v>
+        <v>-1.6923</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3026</v>
+        <v>-4.3382</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5909</v>
+        <v>-1.9692</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7117</v>
+        <v>-2.3689</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1584</v>
+        <v>0.0873</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7103</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.6766</v>
       </c>
       <c r="P11" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4062</v>
+        <v>0.0556</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2692</v>
+        <v>0.2876</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6754</v>
+        <v>-0.232</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.2266</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0017</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.202</v>
+        <v>-4.8426</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.447</v>
+        <v>-4.0433</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.755</v>
+        <v>-0.7993</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7513</v>
+        <v>-0.746</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3463</v>
+        <v>0.3447</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3113</v>
+        <v>-0.3011</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.5715</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1657</v>
+        <v>-0.2298</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.0436</v>
+        <v>-12.3469</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.3321</v>
+        <v>-10.9647</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7111</v>
+        <v>-1.3823</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.4722</v>
+        <v>-14.5023</v>
       </c>
       <c r="H13" t="n">
-        <v>-14.4724</v>
+        <v>-14.5024</v>
       </c>
       <c r="I13" t="n">
-        <v>6.106226635438361e-16</v>
+        <v>-0.0001000000000003776</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.8493</v>
+        <v>-6.119699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.103900000000001</v>
+        <v>-2.2877</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.7458</v>
+        <v>-3.8321</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.622900000000001</v>
+        <v>-8.3827</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.3688</v>
+        <v>-12.215</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7458</v>
+        <v>3.8323</v>
       </c>
       <c r="P13" t="n">
-        <v>3.402600000000001</v>
+        <v>3.4146</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7441</v>
+        <v>-14.7961</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1467</v>
+        <v>18.2107</v>
       </c>
       <c r="S13" t="n">
-        <v>0.983</v>
+        <v>1.6938</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1948</v>
+        <v>1.9229</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2119999999999998</v>
+        <v>-0.229</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.956700000000001</v>
+        <v>-2.9529</v>
       </c>
       <c r="W13" t="n">
-        <v>8.066600000000001</v>
+        <v>8.028300000000002</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.0233</v>
+        <v>-10.981</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8214</v>
+        <v>6.6761</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8246</v>
+        <v>3.3955</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9968</v>
+        <v>3.2806</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3562</v>
+        <v>3.3696</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7892</v>
+        <v>0.7952</v>
       </c>
       <c r="I14" t="n">
-        <v>2.567</v>
+        <v>2.5744</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2487</v>
+        <v>2.2346</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9799</v>
+        <v>0.9685</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1074</v>
+        <v>1.1351</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6028</v>
+        <v>0.2382</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6775</v>
+        <v>-0.0863</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0747</v>
+        <v>0.3245</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7758</v>
+        <v>4.6403</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9485</v>
+        <v>2.1056</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8273</v>
+        <v>2.5347</v>
       </c>
       <c r="G15" t="n">
         <v>2.5438</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3016</v>
+        <v>1.2984</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2422</v>
+        <v>1.2455</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0846</v>
+        <v>2.0697</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4129</v>
+        <v>1.3994</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4592</v>
+        <v>0.4741</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>2.232</v>
+        <v>1.0965</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4517</v>
+        <v>0.6293</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7803</v>
+        <v>0.4672</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5834</v>
+        <v>2.7644</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5914</v>
+        <v>1.3167</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9921</v>
+        <v>1.4477</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3534</v>
+        <v>2.3577</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0952</v>
+        <v>1.0943</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2582</v>
+        <v>1.2634</v>
       </c>
       <c r="J16" t="n">
-        <v>1.155</v>
+        <v>1.1197</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0755</v>
+        <v>0.0475</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1984</v>
+        <v>1.2381</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0197</v>
+        <v>1.0468</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3578</v>
+        <v>-0.1868</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4779</v>
+        <v>0.2457</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8357</v>
+        <v>-0.4325</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3945</v>
+        <v>2.5246</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8009</v>
+        <v>2.4755</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4064</v>
+        <v>0.0491</v>
       </c>
       <c r="G17" t="n">
-        <v>5.325</v>
+        <v>5.3431</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0344</v>
+        <v>5.0402</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2906</v>
+        <v>0.3029</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6143</v>
+        <v>4.5933</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5024</v>
+        <v>4.4816</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7107</v>
+        <v>0.7498</v>
       </c>
       <c r="N17" t="n">
-        <v>0.532</v>
+        <v>0.5586</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9305</v>
+        <v>-0.8185</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2521</v>
+        <v>-0.544</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6784</v>
+        <v>-0.2745</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1911</v>
+        <v>1.257</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1896</v>
+        <v>0.1801</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0015</v>
+        <v>1.077</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6393</v>
+        <v>1.6448</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0103</v>
+        <v>1.0131</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4629</v>
+        <v>1.4576</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8658</v>
+        <v>0.8618</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1764</v>
+        <v>0.1871</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0054</v>
+        <v>0.0675</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1446</v>
+        <v>0.2069</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5315</v>
+        <v>1.0501</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2607</v>
+        <v>2.0921</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2709</v>
+        <v>-1.042</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6404</v>
+        <v>1.6935</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1473</v>
+        <v>1.9156</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4931</v>
+        <v>-0.2221</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1083</v>
+        <v>1.5196</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6407</v>
+        <v>1.1549</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.749</v>
+        <v>0.3647</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5321</v>
+        <v>0.174</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.788</v>
+        <v>0.7608</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2559</v>
+        <v>-0.5868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3327</v>
+        <v>-0.2369</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.0278</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0363</v>
+        <v>-0.2647</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3856</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8683</v>
+        <v>0.0199</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3386</v>
+        <v>0.6021</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6962</v>
+        <v>-0.6314</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9148</v>
+        <v>-0.1384</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2186</v>
+        <v>-0.4931</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5307</v>
+        <v>-0.1146</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1602</v>
+        <v>0.6378</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3705</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1655</v>
+        <v>-0.5168</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7546</v>
+        <v>-0.7761</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5891</v>
+        <v>0.2593</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7543</v>
+        <v>0.4112</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>0.1345</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5456</v>
+        <v>0.2766</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1502</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4063</v>
+        <v>-0.0866</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5565</v>
+        <v>0.704</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9563</v>
+        <v>-1.9669</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9003</v>
+        <v>-1.904</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.056</v>
+        <v>-0.0629</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.507</v>
+        <v>-1.5371</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9391</v>
+        <v>-0.9555</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4494</v>
+        <v>-0.4298</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8934</v>
+        <v>-0.4158</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3551</v>
+        <v>-0.232</v>
       </c>
       <c r="V21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.2253</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7867</v>
+        <v>-0.672</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8532</v>
+        <v>0.8972</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0375</v>
+        <v>0.0401</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5093</v>
+        <v>0.5139</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4718</v>
+        <v>-0.4738</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7546</v>
+        <v>0.7608</v>
       </c>
       <c r="N22" t="n">
-        <v>0.44</v>
+        <v>0.4449</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1031</v>
+        <v>0.0455</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3116</v>
+        <v>-0.8529</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4962</v>
+        <v>0.4099</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1846</v>
+        <v>-1.2628</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1406</v>
+        <v>1.8169</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4041</v>
+        <v>3.8713</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2635</v>
+        <v>-2.0544</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.335</v>
+        <v>0.6935</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7926</v>
+        <v>2.6233</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1276</v>
+        <v>-1.9298</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4757</v>
+        <v>1.1234</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6115</v>
+        <v>1.2481</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2451</v>
+        <v>-0.4422</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6684</v>
+        <v>-0.1862</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5767</v>
+        <v>-0.256</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0.7071</v>
+        <v>2.1789</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2249</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3826</v>
+        <v>-2.1381</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4579</v>
+        <v>-4.1411</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8405</v>
+        <v>2.0031</v>
       </c>
       <c r="G24" t="n">
-        <v>1.8172</v>
+        <v>0.1342</v>
       </c>
       <c r="H24" t="n">
-        <v>3.867</v>
+        <v>1.399</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0498</v>
+        <v>-1.2647</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7284</v>
+        <v>-0.3719</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6424</v>
+        <v>0.7682</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.914</v>
+        <v>-1.1401</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0888</v>
+        <v>0.5062</v>
       </c>
       <c r="N24" t="n">
-        <v>1.2247</v>
+        <v>0.6308</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.973</v>
+        <v>0.4381</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1875</v>
+        <v>0.0809</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7855</v>
+        <v>0.3572</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>0.9317</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1853</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.278</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3067</v>
+        <v>-2.7628</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5415</v>
+        <v>-5.7133</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2348</v>
+        <v>2.9505</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.84</v>
+        <v>-1.8432</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0247</v>
+        <v>-0.0149</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8153</v>
+        <v>-1.8283</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5343</v>
+        <v>-2.561</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.7003</v>
+        <v>-2.7194</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6943</v>
+        <v>0.7178</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O25" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8166</v>
+        <v>0.3858</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3176</v>
+        <v>0.2018</v>
       </c>
       <c r="U25" t="n">
-        <v>0.499</v>
+        <v>0.184</v>
       </c>
       <c r="V25" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W25" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.04330000000001</v>
+        <v>14.62339999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.711200000000001</v>
+        <v>1.382299999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>11.3322</v>
+        <v>13.2412</v>
       </c>
       <c r="G26" t="n">
-        <v>14.4725</v>
+        <v>14.5022</v>
       </c>
       <c r="H26" t="n">
-        <v>14.4724</v>
+        <v>14.5023</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0002000000000010882</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>8.622899999999998</v>
+        <v>8.382699999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>12.3687</v>
+        <v>12.2148</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.7456</v>
+        <v>-3.8321</v>
       </c>
       <c r="M26" t="n">
-        <v>5.8495</v>
+        <v>6.1198</v>
       </c>
       <c r="N26" t="n">
-        <v>2.103600000000001</v>
+        <v>2.287599999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>3.7456</v>
+        <v>3.8322</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.402300000000001</v>
+        <v>-3.414300000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R26" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9830999999999996</v>
+        <v>0.5825999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2118</v>
+        <v>0.2289999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1949</v>
+        <v>0.3534</v>
       </c>
       <c r="V26" t="n">
-        <v>2.9566</v>
+        <v>2.952800000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>11.0233</v>
+        <v>10.9809</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.066599999999999</v>
+        <v>-8.0281</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104500_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104500_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.9904</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.981</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104500_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.0281</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
